--- a/themes/phoneCC.xlsx
+++ b/themes/phoneCC.xlsx
@@ -559,12 +559,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для уточнения информации по звонку из банка напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">    NotAuthorized: Для уточнения информации по звонку из банка напишите в чат приложения [«Уралсиб Онлайн»](https://uralsib.ru/online) или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>убран двойной пробел; добавлена точка в конце предложения</t>
+          <t>убран двойной пробел</t>
         </is>
       </c>
     </row>
